--- a/docs/sample_data/marks_sample.xlsx
+++ b/docs/sample_data/marks_sample.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,14 +468,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -494,14 +494,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>58.5</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -515,19 +515,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SU2026-0003</t>
+          <t>SU2026-0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Geography</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -541,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SU2026-0003</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SU2026-0009</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -593,19 +593,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SU2026-0009</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Geography</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -619,19 +619,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SU2026-0010</t>
+          <t>SU2026-0003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -645,24 +645,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SU2026-0010</t>
+          <t>SU2026-0003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SU2026-0003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
